--- a/observations/phobos_deimos/phobos_deimos.xlsx
+++ b/observations/phobos_deimos/phobos_deimos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iant\Documents\PROGRAMS\nomad_obs\observations\phobos_deimos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B11E37-A911-4298-AF65-D40D884AC4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727AB90A-1DAA-4CFF-B10B-84F2D96BA483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="212">
   <si>
     <t>PHOBOS DEIMOS COP ROWS</t>
   </si>
@@ -669,6 +669,9 @@
   </si>
   <si>
     <t>20240203_215635</t>
+  </si>
+  <si>
+    <t>2026-02-26T18:55:30</t>
   </si>
 </sst>
 </file>
@@ -956,7 +959,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1168,6 +1171,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1180,21 +1189,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1478,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V113"/>
+  <dimension ref="A1:V114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1499,16 +1493,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="M1" s="85" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="M1" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J2" s="72" t="s">
@@ -1519,12 +1513,12 @@
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
+      <c r="D3" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
       <c r="J3" s="72" t="s">
@@ -2978,11 +2972,11 @@
       <c r="J36" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="M36" s="85" t="s">
-        <v>6</v>
-      </c>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85"/>
+      <c r="M36" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="N36" s="89"/>
+      <c r="O36" s="89"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
@@ -4086,11 +4080,11 @@
       <c r="J62" s="76" t="s">
         <v>151</v>
       </c>
-      <c r="N62" s="85" t="s">
-        <v>6</v>
-      </c>
-      <c r="O62" s="85"/>
-      <c r="P62" s="85"/>
+      <c r="N62" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="O62" s="89"/>
+      <c r="P62" s="89"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
@@ -4366,7 +4360,7 @@
       <c r="I69" s="6">
         <v>235</v>
       </c>
-      <c r="J69" s="89" t="s">
+      <c r="J69" s="49" t="s">
         <v>158</v>
       </c>
       <c r="M69">
@@ -4410,7 +4404,7 @@
       <c r="I70" s="9">
         <v>235</v>
       </c>
-      <c r="J70" s="90" t="s">
+      <c r="J70" s="50" t="s">
         <v>159</v>
       </c>
       <c r="N70" s="23" t="s">
@@ -4445,7 +4439,7 @@
       <c r="I71" s="6">
         <v>235</v>
       </c>
-      <c r="J71" s="89" t="s">
+      <c r="J71" s="49" t="s">
         <v>188</v>
       </c>
       <c r="K71" t="s">
@@ -4480,7 +4474,7 @@
       <c r="I72" s="6">
         <v>235</v>
       </c>
-      <c r="J72" s="89" t="s">
+      <c r="J72" s="49" t="s">
         <v>210</v>
       </c>
       <c r="M72" s="15"/>
@@ -4520,7 +4514,7 @@
       <c r="I73" s="9">
         <v>235</v>
       </c>
-      <c r="J73" s="90" t="s">
+      <c r="J73" s="50" t="s">
         <v>209</v>
       </c>
       <c r="M73" s="12" t="s">
@@ -4579,7 +4573,7 @@
       <c r="I74" s="52">
         <v>235</v>
       </c>
-      <c r="J74" s="91" t="s">
+      <c r="J74" s="26" t="s">
         <v>208</v>
       </c>
       <c r="M74" s="15">
@@ -4639,7 +4633,7 @@
       <c r="I75" s="6">
         <v>235</v>
       </c>
-      <c r="J75" s="92" t="s">
+      <c r="J75" s="27" t="s">
         <v>207</v>
       </c>
       <c r="M75" s="1">
@@ -4696,7 +4690,7 @@
       <c r="I76" s="6">
         <v>235</v>
       </c>
-      <c r="J76" s="92" t="s">
+      <c r="J76" s="27" t="s">
         <v>206</v>
       </c>
       <c r="M76" s="41">
@@ -4753,7 +4747,7 @@
       <c r="I77" s="6">
         <v>235</v>
       </c>
-      <c r="J77" s="92" t="s">
+      <c r="J77" s="27" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4785,7 +4779,7 @@
       <c r="I78" s="9">
         <v>235</v>
       </c>
-      <c r="J78" s="93" t="s">
+      <c r="J78" s="84" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4817,7 +4811,7 @@
       <c r="I79" s="75">
         <v>235</v>
       </c>
-      <c r="J79" s="94" t="s">
+      <c r="J79" s="85" t="s">
         <v>203</v>
       </c>
     </row>
@@ -4849,7 +4843,7 @@
       <c r="I80" s="52">
         <v>235</v>
       </c>
-      <c r="J80" s="91" t="s">
+      <c r="J80" s="26" t="s">
         <v>202</v>
       </c>
     </row>
@@ -4881,7 +4875,7 @@
       <c r="I81" s="1">
         <v>235</v>
       </c>
-      <c r="J81" s="92" t="s">
+      <c r="J81" s="27" t="s">
         <v>201</v>
       </c>
       <c r="M81" s="61"/>
@@ -4923,7 +4917,7 @@
       <c r="I82" s="1">
         <v>235</v>
       </c>
-      <c r="J82" s="92" t="s">
+      <c r="J82" s="27" t="s">
         <v>200</v>
       </c>
       <c r="M82" s="58">
@@ -4983,7 +4977,7 @@
       <c r="I83" s="1">
         <v>235</v>
       </c>
-      <c r="J83" s="92" t="s">
+      <c r="J83" s="27" t="s">
         <v>199</v>
       </c>
       <c r="M83" s="58">
@@ -5043,7 +5037,7 @@
       <c r="I84" s="16">
         <v>235</v>
       </c>
-      <c r="J84" s="95" t="s">
+      <c r="J84" s="86" t="s">
         <v>198</v>
       </c>
       <c r="M84" s="58">
@@ -5100,7 +5094,7 @@
       <c r="I85" s="8">
         <v>235</v>
       </c>
-      <c r="J85" s="96" t="s">
+      <c r="J85" s="87" t="s">
         <v>197</v>
       </c>
       <c r="M85" s="58">
@@ -5157,7 +5151,7 @@
       <c r="I86" s="52">
         <v>235</v>
       </c>
-      <c r="J86" s="95" t="s">
+      <c r="J86" s="86" t="s">
         <v>196</v>
       </c>
       <c r="M86" s="59">
@@ -5214,7 +5208,7 @@
       <c r="I87" s="6">
         <v>235</v>
       </c>
-      <c r="J87" s="97" t="s">
+      <c r="J87" s="88" t="s">
         <v>195</v>
       </c>
       <c r="M87" s="2"/>
@@ -5252,7 +5246,7 @@
       <c r="I88" s="6">
         <v>235</v>
       </c>
-      <c r="J88" s="97" t="s">
+      <c r="J88" s="88" t="s">
         <v>194</v>
       </c>
       <c r="M88" s="58">
@@ -5309,7 +5303,7 @@
       <c r="I89" s="9">
         <v>235</v>
       </c>
-      <c r="J89" s="96" t="s">
+      <c r="J89" s="87" t="s">
         <v>193</v>
       </c>
       <c r="M89" s="58">
@@ -5366,7 +5360,7 @@
       <c r="I90" s="52">
         <v>235</v>
       </c>
-      <c r="J90" s="95" t="s">
+      <c r="J90" s="86" t="s">
         <v>192</v>
       </c>
       <c r="M90" s="58"/>
@@ -5400,7 +5394,7 @@
       <c r="I91" s="6">
         <v>235</v>
       </c>
-      <c r="J91" s="97" t="s">
+      <c r="J91" s="88" t="s">
         <v>191</v>
       </c>
       <c r="M91" s="59">
@@ -5457,7 +5451,7 @@
       <c r="I92" s="6">
         <v>235</v>
       </c>
-      <c r="J92" s="97" t="s">
+      <c r="J92" s="88" t="s">
         <v>190</v>
       </c>
     </row>
@@ -5489,7 +5483,7 @@
       <c r="I93" s="9">
         <v>235</v>
       </c>
-      <c r="J93" s="96" t="s">
+      <c r="J93" s="87" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5521,7 +5515,7 @@
       <c r="I94" s="52">
         <v>235</v>
       </c>
-      <c r="J94" s="91" t="s">
+      <c r="J94" s="26" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5553,7 +5547,7 @@
       <c r="I95" s="9">
         <v>235</v>
       </c>
-      <c r="J95" s="93" t="s">
+      <c r="J95" s="84" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5585,7 +5579,7 @@
       <c r="I96" s="6">
         <v>235</v>
       </c>
-      <c r="J96" s="95" t="s">
+      <c r="J96" s="86" t="s">
         <v>184</v>
       </c>
     </row>
@@ -5617,7 +5611,7 @@
       <c r="I97" s="6">
         <v>235</v>
       </c>
-      <c r="J97" s="97" t="s">
+      <c r="J97" s="88" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5649,7 +5643,7 @@
       <c r="I98" s="9">
         <v>235</v>
       </c>
-      <c r="J98" s="96" t="s">
+      <c r="J98" s="87" t="s">
         <v>182</v>
       </c>
     </row>
@@ -5681,7 +5675,7 @@
       <c r="I99" s="52">
         <v>235</v>
       </c>
-      <c r="J99" s="91" t="s">
+      <c r="J99" s="26" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5713,7 +5707,7 @@
       <c r="I100" s="6">
         <v>235</v>
       </c>
-      <c r="J100" s="92" t="s">
+      <c r="J100" s="27" t="s">
         <v>180</v>
       </c>
     </row>
@@ -5745,7 +5739,7 @@
       <c r="I101" s="9">
         <v>235</v>
       </c>
-      <c r="J101" s="93" t="s">
+      <c r="J101" s="84" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5777,7 +5771,7 @@
       <c r="I102" s="9">
         <v>235</v>
       </c>
-      <c r="J102" s="93" t="s">
+      <c r="J102" s="84" t="s">
         <v>178</v>
       </c>
     </row>
@@ -6163,6 +6157,41 @@
         <v>165</v>
       </c>
       <c r="K113" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="4">
+        <v>103</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D114" s="15">
+        <v>60</v>
+      </c>
+      <c r="E114" s="16">
+        <v>4</v>
+      </c>
+      <c r="F114" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G114" s="52">
+        <v>12</v>
+      </c>
+      <c r="H114" s="16">
+        <v>3951</v>
+      </c>
+      <c r="I114" s="52">
+        <v>235</v>
+      </c>
+      <c r="J114" s="83" t="s">
+        <v>211</v>
+      </c>
+      <c r="K114" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6175,7 +6204,7 @@
     <mergeCell ref="N62:P62"/>
   </mergeCells>
   <conditionalFormatting sqref="H5">
-    <cfRule type="iconSet" priority="127">
+    <cfRule type="iconSet" priority="128">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6183,7 +6212,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="128">
+    <cfRule type="iconSet" priority="129">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6193,7 +6222,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H30 H32:H35">
-    <cfRule type="iconSet" priority="86">
+    <cfRule type="iconSet" priority="87">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6201,7 +6230,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="87">
+    <cfRule type="iconSet" priority="88">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6211,7 +6240,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="iconSet" priority="83">
+    <cfRule type="iconSet" priority="84">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6219,7 +6248,7 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="82">
+    <cfRule type="iconSet" priority="83">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6229,7 +6258,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H36:H37">
-    <cfRule type="iconSet" priority="77">
+    <cfRule type="iconSet" priority="78">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6237,7 +6266,7 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="76">
+    <cfRule type="iconSet" priority="77">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6247,7 +6276,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:H39">
-    <cfRule type="iconSet" priority="71">
+    <cfRule type="iconSet" priority="72">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6255,7 +6284,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="72">
+    <cfRule type="iconSet" priority="73">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6265,7 +6294,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="iconSet" priority="66">
+    <cfRule type="iconSet" priority="67">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6273,7 +6302,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="67">
+    <cfRule type="iconSet" priority="68">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6283,7 +6312,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:H42">
-    <cfRule type="iconSet" priority="62">
+    <cfRule type="iconSet" priority="63">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6291,7 +6320,7 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="61">
+    <cfRule type="iconSet" priority="62">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6301,7 +6330,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H43">
-    <cfRule type="iconSet" priority="57">
+    <cfRule type="iconSet" priority="58">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6309,7 +6338,7 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="56">
+    <cfRule type="iconSet" priority="57">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6319,7 +6348,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H44">
-    <cfRule type="iconSet" priority="51">
+    <cfRule type="iconSet" priority="52">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6327,7 +6356,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="52">
+    <cfRule type="iconSet" priority="53">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6337,7 +6366,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45">
-    <cfRule type="iconSet" priority="46">
+    <cfRule type="iconSet" priority="47">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6345,7 +6374,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="47">
+    <cfRule type="iconSet" priority="48">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6355,7 +6384,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H46">
-    <cfRule type="iconSet" priority="41">
+    <cfRule type="iconSet" priority="42">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6363,7 +6392,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="42">
+    <cfRule type="iconSet" priority="43">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6373,7 +6402,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49">
-    <cfRule type="iconSet" priority="36">
+    <cfRule type="iconSet" priority="37">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6381,7 +6410,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="37">
+    <cfRule type="iconSet" priority="38">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6391,6 +6420,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I55">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I56">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -6402,7 +6443,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I56">
+  <conditionalFormatting sqref="I57">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -6414,7 +6455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I57">
+  <conditionalFormatting sqref="I58">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -6426,8 +6467,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I58">
-    <cfRule type="colorScale" priority="29">
+  <conditionalFormatting sqref="I59">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6438,7 +6479,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I59">
+  <conditionalFormatting sqref="I60">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -6450,7 +6491,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I60">
+  <conditionalFormatting sqref="I61">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -6462,7 +6503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I61">
+  <conditionalFormatting sqref="I62">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -6474,7 +6515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I62">
+  <conditionalFormatting sqref="I63">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -6486,7 +6527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I63">
+  <conditionalFormatting sqref="I64">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -6498,7 +6539,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I64">
+  <conditionalFormatting sqref="I65">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -6510,7 +6551,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I65">
+  <conditionalFormatting sqref="I66">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -6522,7 +6563,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I66">
+  <conditionalFormatting sqref="I67:I68">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -6534,8 +6575,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I67:I68">
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="I69">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6546,7 +6587,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I69">
+  <conditionalFormatting sqref="I70">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -6558,7 +6599,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I70">
+  <conditionalFormatting sqref="I71">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -6570,7 +6611,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I71">
+  <conditionalFormatting sqref="I72">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -6582,7 +6623,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72">
+  <conditionalFormatting sqref="I73">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -6594,7 +6635,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I73">
+  <conditionalFormatting sqref="I74:I93">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -6606,7 +6647,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I74:I93">
+  <conditionalFormatting sqref="I94:I95">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -6618,7 +6659,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I94:I95">
+  <conditionalFormatting sqref="I96">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -6630,7 +6671,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96">
+  <conditionalFormatting sqref="I97">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -6642,7 +6683,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I97">
+  <conditionalFormatting sqref="I98">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6654,7 +6695,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I98">
+  <conditionalFormatting sqref="I99:I102">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6666,7 +6707,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99:I102">
+  <conditionalFormatting sqref="I103:I108">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6678,7 +6719,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I103:I108">
+  <conditionalFormatting sqref="I109">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6690,7 +6731,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
+  <conditionalFormatting sqref="I110">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6702,7 +6743,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I110">
+  <conditionalFormatting sqref="I111">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6714,7 +6755,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I111">
+  <conditionalFormatting sqref="I112">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6726,7 +6767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I112">
+  <conditionalFormatting sqref="I113">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6738,7 +6779,349 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I113">
+  <conditionalFormatting sqref="I5:J5">
+    <cfRule type="colorScale" priority="125">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="127">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:J22 I47:J48 I24:J35 I23 J16:J31 I50:J52 I53:I54">
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:J9">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10:J22 I24:J35 I23 J16:J31">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I36:J37">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I38:J39">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I40:J40">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I41:J42">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I43:J43">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I44:J44">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I45:J45">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46:J46">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I49:J49">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I114">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6750,348 +7133,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:J5">
-    <cfRule type="colorScale" priority="124">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="126">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:J22 I47:J48 I24:J35 I23 J16:J31 I50:J52 I53:I54">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J9">
-    <cfRule type="colorScale" priority="89">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10:J22 I24:J35 I23 J16:J31">
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I36:J37">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I38:J39">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40:J40">
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I41:J42">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43:J43">
-    <cfRule type="colorScale" priority="55">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I44:J44">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I45:J45">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I46:J46">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49:J49">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/observations/phobos_deimos/phobos_deimos.xlsx
+++ b/observations/phobos_deimos/phobos_deimos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iant\Documents\PROGRAMS\nomad_obs\observations\phobos_deimos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727AB90A-1DAA-4CFF-B10B-84F2D96BA483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF174CD-6E9A-429E-AF57-314523C59947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="216">
   <si>
     <t>PHOBOS DEIMOS COP ROWS</t>
   </si>
@@ -672,6 +672,18 @@
   </si>
   <si>
     <t>2026-02-26T18:55:30</t>
+  </si>
+  <si>
+    <t>2026-03-29T10:52:47</t>
+  </si>
+  <si>
+    <t>2026-04-01T07:39:29</t>
+  </si>
+  <si>
+    <t>2026-04-04T04:26:20</t>
+  </si>
+  <si>
+    <t>2026-04-10T13:42:46</t>
   </si>
 </sst>
 </file>
@@ -959,7 +971,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1189,6 +1201,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1472,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V114"/>
+  <dimension ref="A1:V118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -6126,7 +6142,7 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A113" s="4">
+      <c r="A113" s="7">
         <v>98</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -6176,22 +6192,162 @@
       <c r="E114" s="16">
         <v>4</v>
       </c>
-      <c r="F114" s="16" t="s">
+      <c r="F114" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="G114" s="52">
-        <v>12</v>
-      </c>
-      <c r="H114" s="16">
+      <c r="G114" s="75">
+        <v>12</v>
+      </c>
+      <c r="H114" s="74">
         <v>3951</v>
       </c>
-      <c r="I114" s="52">
-        <v>235</v>
-      </c>
-      <c r="J114" s="83" t="s">
+      <c r="I114" s="75">
+        <v>235</v>
+      </c>
+      <c r="J114" s="94" t="s">
         <v>211</v>
       </c>
       <c r="K114" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="15">
+        <v>104</v>
+      </c>
+      <c r="B115" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D115" s="15">
+        <v>60</v>
+      </c>
+      <c r="E115" s="16">
+        <v>6</v>
+      </c>
+      <c r="F115" s="93" t="s">
+        <v>143</v>
+      </c>
+      <c r="G115" s="6">
+        <v>12</v>
+      </c>
+      <c r="H115" s="1">
+        <v>3928</v>
+      </c>
+      <c r="I115" s="6">
+        <v>235</v>
+      </c>
+      <c r="J115" s="83" t="s">
+        <v>212</v>
+      </c>
+      <c r="K115" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="4">
+        <v>104</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D116" s="4">
+        <v>60</v>
+      </c>
+      <c r="E116" s="1">
+        <v>6</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G116" s="6">
+        <v>12</v>
+      </c>
+      <c r="H116" s="1">
+        <v>3928</v>
+      </c>
+      <c r="I116" s="6">
+        <v>235</v>
+      </c>
+      <c r="J116" s="83" t="s">
+        <v>213</v>
+      </c>
+      <c r="K116" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
+        <v>104</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D117" s="4">
+        <v>60</v>
+      </c>
+      <c r="E117" s="1">
+        <v>6</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G117" s="6">
+        <v>12</v>
+      </c>
+      <c r="H117" s="1">
+        <v>3928</v>
+      </c>
+      <c r="I117" s="6">
+        <v>235</v>
+      </c>
+      <c r="J117" s="83" t="s">
+        <v>214</v>
+      </c>
+      <c r="K117" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="4">
+        <v>104</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D118" s="7">
+        <v>60</v>
+      </c>
+      <c r="E118" s="8">
+        <v>6</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G118" s="9">
+        <v>12</v>
+      </c>
+      <c r="H118" s="8">
+        <v>3928</v>
+      </c>
+      <c r="I118" s="9">
+        <v>235</v>
+      </c>
+      <c r="J118" s="82" t="s">
+        <v>215</v>
+      </c>
+      <c r="K118" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6204,7 +6360,7 @@
     <mergeCell ref="N62:P62"/>
   </mergeCells>
   <conditionalFormatting sqref="H5">
-    <cfRule type="iconSet" priority="128">
+    <cfRule type="iconSet" priority="132">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6212,7 +6368,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="129">
+    <cfRule type="iconSet" priority="133">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6222,6 +6378,24 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H30 H32:H35">
+    <cfRule type="iconSet" priority="91">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="3810"/>
+        <cfvo type="num" val="3850"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="92">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
     <cfRule type="iconSet" priority="87">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
@@ -6239,8 +6413,16 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="iconSet" priority="84">
+  <conditionalFormatting sqref="H36:H37">
+    <cfRule type="iconSet" priority="81">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="3810"/>
+        <cfvo type="num" val="3850"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="82">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6248,7 +6430,9 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="83">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38:H39">
+    <cfRule type="iconSet" priority="76">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6256,9 +6440,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H36:H37">
-    <cfRule type="iconSet" priority="78">
+    <cfRule type="iconSet" priority="77">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6266,7 +6448,9 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="77">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40">
+    <cfRule type="iconSet" priority="71">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6274,9 +6458,17 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
+    <cfRule type="iconSet" priority="72">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38:H39">
-    <cfRule type="iconSet" priority="72">
+  <conditionalFormatting sqref="H41:H42">
+    <cfRule type="iconSet" priority="66">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6284,7 +6476,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="73">
+    <cfRule type="iconSet" priority="67">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6293,8 +6485,8 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H40">
-    <cfRule type="iconSet" priority="67">
+  <conditionalFormatting sqref="H43">
+    <cfRule type="iconSet" priority="61">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6302,7 +6494,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="68">
+    <cfRule type="iconSet" priority="62">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6311,8 +6503,16 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H41:H42">
-    <cfRule type="iconSet" priority="63">
+  <conditionalFormatting sqref="H44">
+    <cfRule type="iconSet" priority="56">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="3810"/>
+        <cfvo type="num" val="3850"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="57">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6320,7 +6520,9 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="62">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H45">
+    <cfRule type="iconSet" priority="51">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6328,9 +6530,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H43">
-    <cfRule type="iconSet" priority="58">
+    <cfRule type="iconSet" priority="52">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6338,7 +6538,9 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="57">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H46">
+    <cfRule type="iconSet" priority="46">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6346,9 +6548,17 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
+    <cfRule type="iconSet" priority="47">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H44">
-    <cfRule type="iconSet" priority="52">
+  <conditionalFormatting sqref="H49">
+    <cfRule type="iconSet" priority="41">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6356,7 +6566,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="53">
+    <cfRule type="iconSet" priority="42">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6365,62 +6575,8 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H45">
-    <cfRule type="iconSet" priority="47">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="500"/>
-        <cfvo type="num" val="3810"/>
-        <cfvo type="num" val="3850"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="iconSet" priority="48">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="25"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="percent" val="75"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H46">
-    <cfRule type="iconSet" priority="42">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="500"/>
-        <cfvo type="num" val="3810"/>
-        <cfvo type="num" val="3850"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="iconSet" priority="43">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="25"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="percent" val="75"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H49">
-    <cfRule type="iconSet" priority="37">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="500"/>
-        <cfvo type="num" val="3810"/>
-        <cfvo type="num" val="3850"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="iconSet" priority="38">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="25"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="percent" val="75"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I55">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6432,6 +6588,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I56">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I57">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I58">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I59">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -6443,7 +6635,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I57">
+  <conditionalFormatting sqref="I60">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -6455,7 +6647,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I58">
+  <conditionalFormatting sqref="I61">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -6467,7 +6659,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I59">
+  <conditionalFormatting sqref="I62">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I63">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
@@ -6479,7 +6683,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I60">
+  <conditionalFormatting sqref="I64">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -6491,7 +6695,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I61">
+  <conditionalFormatting sqref="I65">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -6503,7 +6707,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I62">
+  <conditionalFormatting sqref="I66">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -6515,7 +6719,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I63">
+  <conditionalFormatting sqref="I67:I68">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -6527,19 +6731,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I64">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I65">
+  <conditionalFormatting sqref="I69">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -6551,7 +6743,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I66">
+  <conditionalFormatting sqref="I70">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -6563,7 +6755,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I67:I68">
+  <conditionalFormatting sqref="I71">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -6575,7 +6767,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I69">
+  <conditionalFormatting sqref="I72">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I73">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -6587,7 +6791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I70">
+  <conditionalFormatting sqref="I74:I93">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -6599,7 +6803,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I71">
+  <conditionalFormatting sqref="I94:I95">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -6611,7 +6815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72">
+  <conditionalFormatting sqref="I96">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -6623,7 +6827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I73">
+  <conditionalFormatting sqref="I97">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -6635,7 +6839,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I74:I93">
+  <conditionalFormatting sqref="I98">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -6647,7 +6851,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I94:I95">
+  <conditionalFormatting sqref="I99:I102">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -6659,7 +6863,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96">
+  <conditionalFormatting sqref="I103:I108">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -6671,7 +6875,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I97">
+  <conditionalFormatting sqref="I109">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -6683,7 +6887,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I98">
+  <conditionalFormatting sqref="I110">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6695,7 +6899,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99:I102">
+  <conditionalFormatting sqref="I111">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6707,7 +6911,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I103:I108">
+  <conditionalFormatting sqref="I112">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6719,7 +6923,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
+  <conditionalFormatting sqref="I113">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6731,7 +6935,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I110">
+  <conditionalFormatting sqref="I114">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6743,7 +6947,349 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I111">
+  <conditionalFormatting sqref="I5:J5">
+    <cfRule type="colorScale" priority="129">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="131">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:J22 I47:J48 I24:J35 I23 J16:J31 I50:J52 I53:I54">
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:J9">
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10:J22 I24:J35 I23 J16:J31">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I36:J37">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I38:J39">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I40:J40">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I41:J42">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I43:J43">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I44:J44">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I45:J45">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46:J46">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I49:J49">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I115">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6755,7 +7301,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I112">
+  <conditionalFormatting sqref="I116">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6767,7 +7313,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I113">
+  <conditionalFormatting sqref="I117">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6779,349 +7325,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:J5">
-    <cfRule type="colorScale" priority="125">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="127">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:J22 I47:J48 I24:J35 I23 J16:J31 I50:J52 I53:I54">
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J9">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="89">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10:J22 I24:J35 I23 J16:J31">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I36:J37">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I38:J39">
-    <cfRule type="colorScale" priority="71">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40:J40">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I41:J42">
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43:J43">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="55">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I44:J44">
-    <cfRule type="colorScale" priority="51">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I45:J45">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I46:J46">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49:J49">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I114">
+  <conditionalFormatting sqref="I118">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/observations/phobos_deimos/phobos_deimos.xlsx
+++ b/observations/phobos_deimos/phobos_deimos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iant\Documents\PROGRAMS\nomad_obs\observations\phobos_deimos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF174CD-6E9A-429E-AF57-314523C59947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A397801F-1031-4AF0-A937-C52F181B1E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="220">
   <si>
     <t>PHOBOS DEIMOS COP ROWS</t>
   </si>
@@ -684,6 +684,18 @@
   </si>
   <si>
     <t>2026-04-10T13:42:46</t>
+  </si>
+  <si>
+    <t>2026-05-20T03:51:30</t>
+  </si>
+  <si>
+    <t>2026-05-25T21:24:30</t>
+  </si>
+  <si>
+    <t>2026-05-31T22:49:30</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:27:30</t>
   </si>
 </sst>
 </file>
@@ -1189,6 +1201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1201,10 +1214,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1488,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V118"/>
+  <dimension ref="A1:V122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1509,16 +1519,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="M1" s="89" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="M1" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J2" s="72" t="s">
@@ -1529,12 +1539,12 @@
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="92"/>
+      <c r="D3" s="91" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="93"/>
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
       <c r="J3" s="72" t="s">
@@ -2988,11 +2998,11 @@
       <c r="J36" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="M36" s="89" t="s">
-        <v>6</v>
-      </c>
-      <c r="N36" s="89"/>
-      <c r="O36" s="89"/>
+      <c r="M36" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="N36" s="90"/>
+      <c r="O36" s="90"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
@@ -4096,11 +4106,11 @@
       <c r="J62" s="76" t="s">
         <v>151</v>
       </c>
-      <c r="N62" s="89" t="s">
-        <v>6</v>
-      </c>
-      <c r="O62" s="89"/>
-      <c r="P62" s="89"/>
+      <c r="N62" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="O62" s="90"/>
+      <c r="P62" s="90"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
@@ -6204,7 +6214,7 @@
       <c r="I114" s="75">
         <v>235</v>
       </c>
-      <c r="J114" s="94" t="s">
+      <c r="J114" s="89" t="s">
         <v>211</v>
       </c>
       <c r="K114" t="s">
@@ -6227,7 +6237,7 @@
       <c r="E115" s="16">
         <v>6</v>
       </c>
-      <c r="F115" s="93" t="s">
+      <c r="F115" s="1" t="s">
         <v>143</v>
       </c>
       <c r="G115" s="6">
@@ -6317,7 +6327,7 @@
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="4">
+      <c r="A118" s="7">
         <v>104</v>
       </c>
       <c r="B118" s="8" t="s">
@@ -6348,6 +6358,146 @@
         <v>215</v>
       </c>
       <c r="K118" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
+        <v>106</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D119" s="4">
+        <v>60</v>
+      </c>
+      <c r="E119" s="1">
+        <v>6</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G119" s="6">
+        <v>12</v>
+      </c>
+      <c r="H119" s="1">
+        <v>3936</v>
+      </c>
+      <c r="I119" s="6">
+        <v>235</v>
+      </c>
+      <c r="J119" s="94" t="s">
+        <v>216</v>
+      </c>
+      <c r="K119" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="4">
+        <v>106</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D120" s="4">
+        <v>60</v>
+      </c>
+      <c r="E120" s="1">
+        <v>6</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G120" s="6">
+        <v>12</v>
+      </c>
+      <c r="H120" s="1">
+        <v>3936</v>
+      </c>
+      <c r="I120" s="6">
+        <v>235</v>
+      </c>
+      <c r="J120" s="94" t="s">
+        <v>217</v>
+      </c>
+      <c r="K120" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
+        <v>106</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D121" s="4">
+        <v>60</v>
+      </c>
+      <c r="E121" s="1">
+        <v>6</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G121" s="6">
+        <v>12</v>
+      </c>
+      <c r="H121" s="1">
+        <v>3936</v>
+      </c>
+      <c r="I121" s="6">
+        <v>235</v>
+      </c>
+      <c r="J121" s="94" t="s">
+        <v>218</v>
+      </c>
+      <c r="K121" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="7">
+        <v>106</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D122" s="7">
+        <v>60</v>
+      </c>
+      <c r="E122" s="8">
+        <v>6</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G122" s="9">
+        <v>12</v>
+      </c>
+      <c r="H122" s="8">
+        <v>3936</v>
+      </c>
+      <c r="I122" s="9">
+        <v>235</v>
+      </c>
+      <c r="J122" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="K122" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6360,7 +6510,15 @@
     <mergeCell ref="N62:P62"/>
   </mergeCells>
   <conditionalFormatting sqref="H5">
-    <cfRule type="iconSet" priority="132">
+    <cfRule type="iconSet" priority="134">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="133">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6368,7 +6526,9 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="133">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6:H30 H32:H35">
+    <cfRule type="iconSet" priority="93">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6376,9 +6536,7 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6:H30 H32:H35">
-    <cfRule type="iconSet" priority="91">
+    <cfRule type="iconSet" priority="92">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6386,7 +6544,17 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="92">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="iconSet" priority="88">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="3810"/>
+        <cfvo type="num" val="3850"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="89">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6395,8 +6563,16 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="iconSet" priority="87">
+  <conditionalFormatting sqref="H36:H37">
+    <cfRule type="iconSet" priority="83">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="82">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6404,7 +6580,9 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="88">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38:H39">
+    <cfRule type="iconSet" priority="78">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6412,9 +6590,7 @@
         <cfvo type="percent" val="75"/>
       </iconSet>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H36:H37">
-    <cfRule type="iconSet" priority="81">
+    <cfRule type="iconSet" priority="77">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6422,7 +6598,17 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="82">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40">
+    <cfRule type="iconSet" priority="72">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="3810"/>
+        <cfvo type="num" val="3850"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="73">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6431,8 +6617,8 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38:H39">
-    <cfRule type="iconSet" priority="76">
+  <conditionalFormatting sqref="H41:H42">
+    <cfRule type="iconSet" priority="67">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6440,7 +6626,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="77">
+    <cfRule type="iconSet" priority="68">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6449,8 +6635,8 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H40">
-    <cfRule type="iconSet" priority="71">
+  <conditionalFormatting sqref="H43">
+    <cfRule type="iconSet" priority="62">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6458,7 +6644,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="72">
+    <cfRule type="iconSet" priority="63">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6467,8 +6653,8 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H41:H42">
-    <cfRule type="iconSet" priority="66">
+  <conditionalFormatting sqref="H44">
+    <cfRule type="iconSet" priority="57">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6476,7 +6662,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="67">
+    <cfRule type="iconSet" priority="58">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6485,8 +6671,8 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H43">
-    <cfRule type="iconSet" priority="61">
+  <conditionalFormatting sqref="H45">
+    <cfRule type="iconSet" priority="52">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6494,7 +6680,7 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="62">
+    <cfRule type="iconSet" priority="53">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6503,8 +6689,16 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H44">
-    <cfRule type="iconSet" priority="56">
+  <conditionalFormatting sqref="H46">
+    <cfRule type="iconSet" priority="48">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="47">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="500"/>
@@ -6512,7 +6706,17 @@
         <cfvo type="num" val="3850"/>
       </iconSet>
     </cfRule>
-    <cfRule type="iconSet" priority="57">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H49">
+    <cfRule type="iconSet" priority="42">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="500"/>
+        <cfvo type="num" val="3810"/>
+        <cfvo type="num" val="3850"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="43">
       <iconSet iconSet="4TrafficLights">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="25"/>
@@ -6521,61 +6725,19 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H45">
-    <cfRule type="iconSet" priority="51">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="500"/>
-        <cfvo type="num" val="3810"/>
-        <cfvo type="num" val="3850"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="iconSet" priority="52">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="25"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="percent" val="75"/>
-      </iconSet>
+  <conditionalFormatting sqref="I55">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H46">
-    <cfRule type="iconSet" priority="46">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="500"/>
-        <cfvo type="num" val="3810"/>
-        <cfvo type="num" val="3850"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="iconSet" priority="47">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="25"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="percent" val="75"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H49">
-    <cfRule type="iconSet" priority="41">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="500"/>
-        <cfvo type="num" val="3810"/>
-        <cfvo type="num" val="3850"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="iconSet" priority="42">
-      <iconSet iconSet="4TrafficLights">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="25"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="percent" val="75"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I55">
+  <conditionalFormatting sqref="I56">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -6587,7 +6749,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I56">
+  <conditionalFormatting sqref="I57">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -6599,7 +6761,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I57">
+  <conditionalFormatting sqref="I58">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -6611,8 +6773,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I58">
-    <cfRule type="colorScale" priority="34">
+  <conditionalFormatting sqref="I59">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6623,7 +6785,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I59">
+  <conditionalFormatting sqref="I60">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -6635,7 +6797,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I60">
+  <conditionalFormatting sqref="I61">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -6647,7 +6809,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I61">
+  <conditionalFormatting sqref="I62">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -6659,7 +6821,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I62">
+  <conditionalFormatting sqref="I63">
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -6671,7 +6833,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I63">
+  <conditionalFormatting sqref="I64">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
@@ -6683,7 +6845,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I64">
+  <conditionalFormatting sqref="I65">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -6695,7 +6857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I65">
+  <conditionalFormatting sqref="I66">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -6707,7 +6869,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I66">
+  <conditionalFormatting sqref="I67:I68">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -6719,8 +6881,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I67:I68">
-    <cfRule type="colorScale" priority="24">
+  <conditionalFormatting sqref="I69">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6731,7 +6893,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I69">
+  <conditionalFormatting sqref="I70">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -6743,7 +6905,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I70">
+  <conditionalFormatting sqref="I71">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -6755,7 +6917,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I71">
+  <conditionalFormatting sqref="I72">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -6767,7 +6929,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72">
+  <conditionalFormatting sqref="I73">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -6779,7 +6941,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I73">
+  <conditionalFormatting sqref="I74:I93">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -6791,7 +6953,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I74:I93">
+  <conditionalFormatting sqref="I94:I95">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -6803,7 +6965,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I94:I95">
+  <conditionalFormatting sqref="I96">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -6815,7 +6977,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96">
+  <conditionalFormatting sqref="I97">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -6827,7 +6989,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I97">
+  <conditionalFormatting sqref="I98">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -6839,7 +7001,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I98">
+  <conditionalFormatting sqref="I99:I102">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -6851,7 +7013,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99:I102">
+  <conditionalFormatting sqref="I103:I108">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -6863,7 +7025,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I103:I108">
+  <conditionalFormatting sqref="I109">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -6875,7 +7037,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
+  <conditionalFormatting sqref="I110">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -6887,7 +7049,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I110">
+  <conditionalFormatting sqref="I111">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6899,7 +7061,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I111">
+  <conditionalFormatting sqref="I112">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6911,7 +7073,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I112">
+  <conditionalFormatting sqref="I113">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6923,7 +7085,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I113">
+  <conditionalFormatting sqref="I114">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6935,7 +7097,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I114">
+  <conditionalFormatting sqref="I115">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6947,349 +7109,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:J5">
-    <cfRule type="colorScale" priority="129">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="131">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:J22 I47:J48 I24:J35 I23 J16:J31 I50:J52 I53:I54">
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J9">
-    <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10:J22 I24:J35 I23 J16:J31">
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I36:J37">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I38:J39">
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40:J40">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I41:J42">
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43:J43">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I44:J44">
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="55">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I45:J45">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I46:J46">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49:J49">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I115">
+  <conditionalFormatting sqref="I116">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -7301,7 +7121,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I116">
+  <conditionalFormatting sqref="I117">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7313,7 +7133,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I117">
+  <conditionalFormatting sqref="I118">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7325,7 +7145,349 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I118">
+  <conditionalFormatting sqref="I5:J5">
+    <cfRule type="colorScale" priority="130">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="132">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:J22 I47:J48 I24:J35 I23 J16:J31 I50:J52 I53:I54">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:J9">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10:J22 I24:J35 I23 J16:J31">
+    <cfRule type="colorScale" priority="87">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I36:J37">
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I38:J39">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I40:J40">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I41:J42">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I43:J43">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I44:J44">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I45:J45">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46:J46">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I49:J49">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I119:I122">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
